--- a/data/SEMANA ATUAL/PREMIER.xlsx
+++ b/data/SEMANA ATUAL/PREMIER.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="273">
   <si>
     <t>Sigla Loja</t>
   </si>
@@ -26,6 +26,9 @@
   </si>
   <si>
     <t>21/07/2026 (Ter)</t>
+  </si>
+  <si>
+    <t>22/07/2026 (Qua)</t>
   </si>
   <si>
     <t>ABNO-RJ</t>
@@ -1195,7 +1198,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D269"/>
+  <dimension ref="A1:E269"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.7109375" customWidth="1"/>
@@ -1203,7 +1206,7 @@
     <col min="3" max="3" width="15.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1216,10 +1219,13 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" s="1">
         <v>4747.23</v>
@@ -1227,32 +1233,41 @@
       <c r="D2" s="1">
         <v>4000.309999999999</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="E2" s="1">
+        <v>4016.469999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="1">
-        <v>4582.66</v>
+        <v>4582.659999999999</v>
       </c>
       <c r="D3" s="1">
-        <v>6316.51</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>6316.509999999997</v>
+      </c>
+      <c r="E3" s="1">
+        <v>4166.989999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="1">
-        <v>6065.519999999998</v>
+        <v>6065.52</v>
       </c>
       <c r="D4" s="1">
         <v>7693.26</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="E4" s="1">
+        <v>4917.239999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" s="1">
         <v>6105.41</v>
@@ -1260,21 +1275,27 @@
       <c r="D5" s="1">
         <v>4331.32</v>
       </c>
-    </row>
-    <row r="6" spans="1:4">
+      <c r="E5" s="1">
+        <v>5541.100000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C6" s="1">
         <v>3420.109999999999</v>
       </c>
       <c r="D6" s="1">
-        <v>4445.629999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+        <v>4445.629999999998</v>
+      </c>
+      <c r="E6" s="1">
+        <v>3878.319999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C7" s="1">
         <v>5122.299999999999</v>
@@ -1282,32 +1303,41 @@
       <c r="D7" s="1">
         <v>5853.39</v>
       </c>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="E7" s="1">
+        <v>5133.769999999997</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C8" s="1">
-        <v>3963.23</v>
+        <v>3963.229999999999</v>
       </c>
       <c r="D8" s="1">
         <v>3069.5</v>
       </c>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="E8" s="1">
+        <v>2914.32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C9" s="1">
-        <v>7073.969999999998</v>
+        <v>7073.970000000001</v>
       </c>
       <c r="D9" s="1">
         <v>3497.48</v>
       </c>
-    </row>
-    <row r="10" spans="1:4">
+      <c r="E9" s="1">
+        <v>6415.409999999997</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C10" s="1">
         <v>2433.93</v>
@@ -1315,43 +1345,55 @@
       <c r="D10" s="1">
         <v>2004.48</v>
       </c>
-    </row>
-    <row r="11" spans="1:4">
+      <c r="E10" s="1">
+        <v>1579.9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C11" s="1">
-        <v>9083.070000000002</v>
+        <v>9083.07</v>
       </c>
       <c r="D11" s="1">
-        <v>9512.249999999998</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
+        <v>9512.249999999996</v>
+      </c>
+      <c r="E11" s="1">
+        <v>7779.98</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C12" s="1">
-        <v>6406.07</v>
+        <v>6406.069999999999</v>
       </c>
       <c r="D12" s="1">
         <v>3015.89</v>
       </c>
-    </row>
-    <row r="13" spans="1:4">
+      <c r="E12" s="1">
+        <v>2754.659999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C13" s="1">
         <v>6311.269999999999</v>
       </c>
       <c r="D13" s="1">
-        <v>4143.429999999999</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
+        <v>4143.429999999998</v>
+      </c>
+      <c r="E13" s="1">
+        <v>3645.610000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C14" s="1">
         <v>5627.119999999999</v>
@@ -1359,10 +1401,13 @@
       <c r="D14" s="1">
         <v>3838.52</v>
       </c>
-    </row>
-    <row r="15" spans="1:4">
+      <c r="E14" s="1">
+        <v>4888.619999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C15" s="1">
         <v>10614.26</v>
@@ -1370,10 +1415,13 @@
       <c r="D15" s="1">
         <v>11577.88</v>
       </c>
-    </row>
-    <row r="16" spans="1:4">
+      <c r="E15" s="1">
+        <v>8721.379999999997</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C16" s="1">
         <v>1695.89</v>
@@ -1381,10 +1429,13 @@
       <c r="D16" s="1">
         <v>1570.27</v>
       </c>
-    </row>
-    <row r="17" spans="1:4">
+      <c r="E16" s="1">
+        <v>1099.73</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C17" s="1">
         <v>3442.72</v>
@@ -1392,32 +1443,41 @@
       <c r="D17" s="1">
         <v>4429.99</v>
       </c>
-    </row>
-    <row r="18" spans="1:4">
+      <c r="E17" s="1">
+        <v>3473.58</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C18" s="1">
-        <v>4028.989999999999</v>
+        <v>4028.99</v>
       </c>
       <c r="D18" s="1">
         <v>3433.129999999999</v>
       </c>
-    </row>
-    <row r="19" spans="1:4">
+      <c r="E18" s="1">
+        <v>3505.549999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C19" s="1">
-        <v>3582.47</v>
+        <v>3582.469999999999</v>
       </c>
       <c r="D19" s="1">
         <v>2936.54</v>
       </c>
-    </row>
-    <row r="20" spans="1:4">
+      <c r="E19" s="1">
+        <v>2124.47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C20" s="1">
         <v>6206.48</v>
@@ -1425,10 +1485,13 @@
       <c r="D20" s="1">
         <v>6294.14</v>
       </c>
-    </row>
-    <row r="21" spans="1:4">
+      <c r="E20" s="1">
+        <v>4868.15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C21" s="1">
         <v>2236.9</v>
@@ -1436,10 +1499,13 @@
       <c r="D21" s="1">
         <v>2248.34</v>
       </c>
-    </row>
-    <row r="22" spans="1:4">
+      <c r="E21" s="1">
+        <v>2761.33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C22" s="1">
         <v>373.02</v>
@@ -1447,10 +1513,13 @@
       <c r="D22" s="1">
         <v>664.9299999999999</v>
       </c>
-    </row>
-    <row r="23" spans="1:4">
+      <c r="E22" s="1">
+        <v>1293.36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C23" s="1">
         <v>2807.57</v>
@@ -1458,10 +1527,13 @@
       <c r="D23" s="1">
         <v>4963.2</v>
       </c>
-    </row>
-    <row r="24" spans="1:4">
+      <c r="E23" s="1">
+        <v>2107.67</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C24" s="1">
         <v>1935.69</v>
@@ -1469,21 +1541,27 @@
       <c r="D24" s="1">
         <v>1860.95</v>
       </c>
-    </row>
-    <row r="25" spans="1:4">
+      <c r="E24" s="1">
+        <v>2030.66</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C25" s="1">
-        <v>7650.329999999999</v>
+        <v>7650.33</v>
       </c>
       <c r="D25" s="1">
-        <v>8004.259999999997</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
+        <v>8004.26</v>
+      </c>
+      <c r="E25" s="1">
+        <v>6588.429999999998</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C26" s="1">
         <v>2224.69</v>
@@ -1491,21 +1569,27 @@
       <c r="D26" s="1">
         <v>2094.62</v>
       </c>
-    </row>
-    <row r="27" spans="1:4">
+      <c r="E26" s="1">
+        <v>2066.659999999999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C27" s="1">
-        <v>5534.669999999998</v>
+        <v>5534.67</v>
       </c>
       <c r="D27" s="1">
-        <v>5529.929999999998</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
+        <v>5529.929999999999</v>
+      </c>
+      <c r="E27" s="1">
+        <v>5095.639999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C28" s="1">
         <v>6519.409999999999</v>
@@ -1513,21 +1597,27 @@
       <c r="D28" s="1">
         <v>5708.639999999999</v>
       </c>
-    </row>
-    <row r="29" spans="1:4">
+      <c r="E28" s="1">
+        <v>5473.149999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C29" s="1">
         <v>2515.5</v>
       </c>
       <c r="D29" s="1">
-        <v>2162.420000000001</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
+        <v>2162.42</v>
+      </c>
+      <c r="E29" s="1">
+        <v>1619.03</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C30" s="1">
         <v>2075.3</v>
@@ -1535,76 +1625,97 @@
       <c r="D30" s="1">
         <v>2064.53</v>
       </c>
-    </row>
-    <row r="31" spans="1:4">
+      <c r="E30" s="1">
+        <v>3932.229999999997</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C31" s="1">
-        <v>7163.399999999998</v>
+        <v>7163.4</v>
       </c>
       <c r="D31" s="1">
-        <v>8311.509999999998</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
+        <v>8311.51</v>
+      </c>
+      <c r="E31" s="1">
+        <v>8666.139999999998</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C32" s="1">
-        <v>7000.63</v>
+        <v>7000.629999999998</v>
       </c>
       <c r="D32" s="1">
         <v>6504.65</v>
       </c>
-    </row>
-    <row r="33" spans="1:4">
+      <c r="E32" s="1">
+        <v>7265.209999999999</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C33" s="1">
-        <v>7135.120000000002</v>
+        <v>7135.119999999999</v>
       </c>
       <c r="D33" s="1">
-        <v>4923.409999999999</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
+        <v>5256.41</v>
+      </c>
+      <c r="E33" s="1">
+        <v>8618.15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C34" s="1">
         <v>2590.92</v>
       </c>
       <c r="D34" s="1">
-        <v>4461.79</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
+        <v>4461.790000000001</v>
+      </c>
+      <c r="E34" s="1">
+        <v>2321.25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C35" s="1">
-        <v>4998.199999999999</v>
+        <v>4998.200000000001</v>
       </c>
       <c r="D35" s="1">
-        <v>6025.989999999997</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
+        <v>6025.99</v>
+      </c>
+      <c r="E35" s="1">
+        <v>5688.619999999999</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C36" s="1">
-        <v>8801.98</v>
+        <v>8801.980000000001</v>
       </c>
       <c r="D36" s="1">
         <v>9203.489999999998</v>
       </c>
-    </row>
-    <row r="37" spans="1:4">
+      <c r="E36" s="1">
+        <v>9313.93</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C37" s="1">
         <v>2248.89</v>
@@ -1612,10 +1723,13 @@
       <c r="D37" s="1">
         <v>1098.45</v>
       </c>
-    </row>
-    <row r="38" spans="1:4">
+      <c r="E37" s="1">
+        <v>1441.91</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C38" s="1">
         <v>665.76</v>
@@ -1623,87 +1737,111 @@
       <c r="D38" s="1">
         <v>2417.63</v>
       </c>
-    </row>
-    <row r="39" spans="1:4">
+      <c r="E38" s="1">
+        <v>2498.279999999999</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C39" s="1">
-        <v>7003.089999999997</v>
+        <v>7003.089999999998</v>
       </c>
       <c r="D39" s="1">
         <v>7208.289999999999</v>
       </c>
-    </row>
-    <row r="40" spans="1:4">
+      <c r="E39" s="1">
+        <v>5611.759999999998</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C40" s="1">
         <v>3683.25</v>
       </c>
       <c r="D40" s="1">
-        <v>4856.589999999998</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
+        <v>4856.59</v>
+      </c>
+      <c r="E40" s="1">
+        <v>2835.179999999999</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C41" s="1">
-        <v>6133.47</v>
+        <v>6133.469999999998</v>
       </c>
       <c r="D41" s="1">
-        <v>5357.009999999999</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
+        <v>5357.01</v>
+      </c>
+      <c r="E41" s="1">
+        <v>3498.79</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
       <c r="A42" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C42" s="1">
         <v>2371.78</v>
       </c>
       <c r="D42" s="1">
-        <v>2967.88</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4">
+        <v>2967.879999999999</v>
+      </c>
+      <c r="E42" s="1">
+        <v>1588.24</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
       <c r="A43" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C43" s="1">
         <v>4127.82</v>
       </c>
       <c r="D43" s="1">
-        <v>3821.4</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4">
+        <v>3821.399999999999</v>
+      </c>
+      <c r="E43" s="1">
+        <v>8188.779999999999</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
       <c r="A44" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C44" s="1">
-        <v>8696.710000000001</v>
+        <v>8696.709999999999</v>
       </c>
       <c r="D44" s="1">
-        <v>9053.889999999999</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4">
+        <v>9053.890000000001</v>
+      </c>
+      <c r="E44" s="1">
+        <v>6992.659999999997</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
       <c r="A45" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C45" s="1">
         <v>12249.76</v>
       </c>
       <c r="D45" s="1">
-        <v>8368.959999999999</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4">
+        <v>8368.959999999997</v>
+      </c>
+      <c r="E45" s="1">
+        <v>10375.75</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
       <c r="A46" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C46" s="1">
         <v>2158.07</v>
@@ -1711,32 +1849,41 @@
       <c r="D46" s="1">
         <v>1785.72</v>
       </c>
-    </row>
-    <row r="47" spans="1:4">
+      <c r="E46" s="1">
+        <v>3008.189999999999</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
       <c r="A47" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C47" s="1">
         <v>7192.829999999999</v>
       </c>
       <c r="D47" s="1">
-        <v>4888.109999999999</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4">
+        <v>5148.099999999999</v>
+      </c>
+      <c r="E47" s="1">
+        <v>5270.679999999999</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
       <c r="A48" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C48" s="1">
-        <v>4862.030000000001</v>
+        <v>4862.029999999998</v>
       </c>
       <c r="D48" s="1">
-        <v>8624.58</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4">
+        <v>8624.579999999998</v>
+      </c>
+      <c r="E48" s="1">
+        <v>8033.4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
       <c r="A49" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C49" s="1">
         <v>1001.26</v>
@@ -1744,10 +1891,13 @@
       <c r="D49" s="1">
         <v>2332.05</v>
       </c>
-    </row>
-    <row r="50" spans="1:4">
+      <c r="E49" s="1">
+        <v>1742.5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
       <c r="A50" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C50" s="1">
         <v>3951.609999999999</v>
@@ -1755,32 +1905,41 @@
       <c r="D50" s="1">
         <v>4498.299999999999</v>
       </c>
-    </row>
-    <row r="51" spans="1:4">
+      <c r="E50" s="1">
+        <v>3904.96</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
       <c r="A51" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C51" s="1">
-        <v>3345.4</v>
+        <v>3345.399999999999</v>
       </c>
       <c r="D51" s="1">
         <v>2384.79</v>
       </c>
-    </row>
-    <row r="52" spans="1:4">
+      <c r="E51" s="1">
+        <v>2813.099999999999</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
       <c r="A52" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C52" s="1">
-        <v>4961.509999999999</v>
+        <v>4961.51</v>
       </c>
       <c r="D52" s="1">
         <v>2938.449999999999</v>
       </c>
-    </row>
-    <row r="53" spans="1:4">
+      <c r="E52" s="1">
+        <v>3783.939999999999</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
       <c r="A53" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C53" s="1">
         <v>1235.01</v>
@@ -1788,10 +1947,13 @@
       <c r="D53" s="1">
         <v>2256.9</v>
       </c>
-    </row>
-    <row r="54" spans="1:4">
+      <c r="E53" s="1">
+        <v>1320.56</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
       <c r="A54" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C54" s="1">
         <v>3805.159999999999</v>
@@ -1799,43 +1961,55 @@
       <c r="D54" s="1">
         <v>3027.17</v>
       </c>
-    </row>
-    <row r="55" spans="1:4">
+      <c r="E54" s="1">
+        <v>4978.029999999999</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
       <c r="A55" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C55" s="1">
-        <v>3954.580000000001</v>
+        <v>3954.579999999999</v>
       </c>
       <c r="D55" s="1">
-        <v>3973.539999999999</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4">
+        <v>3973.54</v>
+      </c>
+      <c r="E55" s="1">
+        <v>6954.819999999999</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
       <c r="A56" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C56" s="1">
-        <v>24696.7</v>
+        <v>24696.70000000001</v>
       </c>
       <c r="D56" s="1">
         <v>22617.05000000001</v>
       </c>
-    </row>
-    <row r="57" spans="1:4">
+      <c r="E56" s="1">
+        <v>13859.1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
       <c r="A57" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C57" s="1">
-        <v>5310.119999999999</v>
+        <v>5310.12</v>
       </c>
       <c r="D57" s="1">
         <v>2496.67</v>
       </c>
-    </row>
-    <row r="58" spans="1:4">
+      <c r="E57" s="1">
+        <v>2485.23</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
       <c r="A58" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C58" s="1">
         <v>2111.29</v>
@@ -1843,10 +2017,13 @@
       <c r="D58" s="1">
         <v>2234.76</v>
       </c>
-    </row>
-    <row r="59" spans="1:4">
+      <c r="E58" s="1">
+        <v>3562.549999999998</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
       <c r="A59" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C59" s="1">
         <v>1385.43</v>
@@ -1854,21 +2031,27 @@
       <c r="D59" s="1">
         <v>2009.51</v>
       </c>
-    </row>
-    <row r="60" spans="1:4">
+      <c r="E59" s="1">
+        <v>1427.07</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
       <c r="A60" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C60" s="1">
-        <v>9049.970000000001</v>
+        <v>9049.969999999999</v>
       </c>
       <c r="D60" s="1">
         <v>8634.859999999999</v>
       </c>
-    </row>
-    <row r="61" spans="1:4">
+      <c r="E60" s="1">
+        <v>8415.15</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
       <c r="A61" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C61" s="1">
         <v>1079.09</v>
@@ -1876,21 +2059,27 @@
       <c r="D61" s="1">
         <v>1107.2</v>
       </c>
-    </row>
-    <row r="62" spans="1:4">
+      <c r="E61" s="1">
+        <v>1879.06</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
       <c r="A62" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C62" s="1">
         <v>4702.75</v>
       </c>
       <c r="D62" s="1">
-        <v>4662.180000000001</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4">
+        <v>4662.179999999998</v>
+      </c>
+      <c r="E62" s="1">
+        <v>3715.739999999999</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
       <c r="A63" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C63" s="1">
         <v>4787.909999999999</v>
@@ -1898,21 +2087,27 @@
       <c r="D63" s="1">
         <v>4356.419999999999</v>
       </c>
-    </row>
-    <row r="64" spans="1:4">
+      <c r="E63" s="1">
+        <v>4062.73</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
       <c r="A64" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C64" s="1">
         <v>2226.45</v>
       </c>
       <c r="D64" s="1">
-        <v>514.6600000000001</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4">
+        <v>514.66</v>
+      </c>
+      <c r="E64" s="1">
+        <v>1964.25</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
       <c r="A65" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C65" s="1">
         <v>5289.389999999999</v>
@@ -1920,10 +2115,13 @@
       <c r="D65" s="1">
         <v>2253.21</v>
       </c>
-    </row>
-    <row r="66" spans="1:4">
+      <c r="E65" s="1">
+        <v>2066.58</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
       <c r="A66" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C66" s="1">
         <v>3286.25</v>
@@ -1931,21 +2129,27 @@
       <c r="D66" s="1">
         <v>2251.27</v>
       </c>
-    </row>
-    <row r="67" spans="1:4">
+      <c r="E66" s="1">
+        <v>3978.87</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
       <c r="A67" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C67" s="1">
         <v>4129.02</v>
       </c>
       <c r="D67" s="1">
-        <v>4507.570000000001</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4">
+        <v>4507.569999999999</v>
+      </c>
+      <c r="E67" s="1">
+        <v>3597.439999999999</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
       <c r="A68" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C68" s="1">
         <v>5018.43</v>
@@ -1953,21 +2157,27 @@
       <c r="D68" s="1">
         <v>3973.52</v>
       </c>
-    </row>
-    <row r="69" spans="1:4">
+      <c r="E68" s="1">
+        <v>2848.31</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
       <c r="A69" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C69" s="1">
-        <v>4689.589999999999</v>
+        <v>4689.589999999998</v>
       </c>
       <c r="D69" s="1">
-        <v>4941.359999999999</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4">
+        <v>4941.36</v>
+      </c>
+      <c r="E69" s="1">
+        <v>6333.559999999999</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
       <c r="A70" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C70" s="1">
         <v>2277.690000000001</v>
@@ -1975,10 +2185,13 @@
       <c r="D70" s="1">
         <v>1331.34</v>
       </c>
-    </row>
-    <row r="71" spans="1:4">
+      <c r="E70" s="1">
+        <v>3022.5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
       <c r="A71" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C71" s="1">
         <v>1870.96</v>
@@ -1986,32 +2199,41 @@
       <c r="D71" s="1">
         <v>1624.68</v>
       </c>
-    </row>
-    <row r="72" spans="1:4">
+      <c r="E71" s="1">
+        <v>1836.4</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
       <c r="A72" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C72" s="1">
-        <v>3209.289999999999</v>
+        <v>3209.29</v>
       </c>
       <c r="D72" s="1">
-        <v>2442.4</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4">
+        <v>2442.399999999999</v>
+      </c>
+      <c r="E72" s="1">
+        <v>3192.309999999999</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
       <c r="A73" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C73" s="1">
         <v>2943.619999999999</v>
       </c>
       <c r="D73" s="1">
-        <v>4269.709999999998</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4">
+        <v>4269.709999999999</v>
+      </c>
+      <c r="E73" s="1">
+        <v>3127.22</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
       <c r="A74" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C74" s="1">
         <v>2893.619999999999</v>
@@ -2019,32 +2241,41 @@
       <c r="D74" s="1">
         <v>2128.38</v>
       </c>
-    </row>
-    <row r="75" spans="1:4">
+      <c r="E74" s="1">
+        <v>1442.67</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
       <c r="A75" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C75" s="1">
-        <v>5438.57</v>
+        <v>5438.569999999999</v>
       </c>
       <c r="D75" s="1">
-        <v>2504.07</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4">
+        <v>2504.069999999999</v>
+      </c>
+      <c r="E75" s="1">
+        <v>5811.48</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
       <c r="A76" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C76" s="1">
-        <v>5790.249999999999</v>
+        <v>5790.249999999997</v>
       </c>
       <c r="D76" s="1">
         <v>6208.369999999997</v>
       </c>
-    </row>
-    <row r="77" spans="1:4">
+      <c r="E76" s="1">
+        <v>8234.619999999997</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
       <c r="A77" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C77" s="1">
         <v>4202.589999999999</v>
@@ -2052,43 +2283,55 @@
       <c r="D77" s="1">
         <v>3477.01</v>
       </c>
-    </row>
-    <row r="78" spans="1:4">
+      <c r="E77" s="1">
+        <v>3265.71</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
       <c r="A78" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C78" s="1">
-        <v>4177.169999999999</v>
+        <v>4177.17</v>
       </c>
       <c r="D78" s="1">
         <v>5718.66</v>
       </c>
-    </row>
-    <row r="79" spans="1:4">
+      <c r="E78" s="1">
+        <v>3515.129999999998</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
       <c r="A79" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C79" s="1">
-        <v>4583.450000000001</v>
+        <v>4583.449999999999</v>
       </c>
       <c r="D79" s="1">
-        <v>4774.39</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4">
+        <v>4774.389999999998</v>
+      </c>
+      <c r="E79" s="1">
+        <v>3101.24</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
       <c r="A80" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C80" s="1">
-        <v>3917.01</v>
+        <v>3917.009999999999</v>
       </c>
       <c r="D80" s="1">
-        <v>5143.099999999999</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4">
+        <v>5143.100000000001</v>
+      </c>
+      <c r="E80" s="1">
+        <v>4100.7</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
       <c r="A81" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C81" s="1">
         <v>4026.439999999999</v>
@@ -2096,43 +2339,55 @@
       <c r="D81" s="1">
         <v>1706.03</v>
       </c>
-    </row>
-    <row r="82" spans="1:4">
+      <c r="E81" s="1">
+        <v>3346.92</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
       <c r="A82" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C82" s="1">
-        <v>3185.35</v>
+        <v>3185.350000000001</v>
       </c>
       <c r="D82" s="1">
         <v>2029.15</v>
       </c>
-    </row>
-    <row r="83" spans="1:4">
+      <c r="E82" s="1">
+        <v>3437.320000000001</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
       <c r="A83" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C83" s="1">
         <v>3306.889999999999</v>
       </c>
       <c r="D83" s="1">
-        <v>3932.6</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4">
+        <v>3932.599999999999</v>
+      </c>
+      <c r="E83" s="1">
+        <v>3752.3</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
       <c r="A84" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C84" s="1">
         <v>12391.07</v>
       </c>
       <c r="D84" s="1">
-        <v>10051.9</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4">
+        <v>10150.37</v>
+      </c>
+      <c r="E84" s="1">
+        <v>10306.5</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
       <c r="A85" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C85" s="1">
         <v>4313.399999999999</v>
@@ -2140,10 +2395,13 @@
       <c r="D85" s="1">
         <v>2389.69</v>
       </c>
-    </row>
-    <row r="86" spans="1:4">
+      <c r="E85" s="1">
+        <v>4337.839999999999</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
       <c r="A86" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C86" s="1">
         <v>1846.7</v>
@@ -2151,10 +2409,13 @@
       <c r="D86" s="1">
         <v>1022.9</v>
       </c>
-    </row>
-    <row r="87" spans="1:4">
+      <c r="E86" s="1">
+        <v>700.84</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
       <c r="A87" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C87" s="1">
         <v>2354.39</v>
@@ -2162,54 +2423,69 @@
       <c r="D87" s="1">
         <v>1760.22</v>
       </c>
-    </row>
-    <row r="88" spans="1:4">
+      <c r="E87" s="1">
+        <v>1099.65</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
       <c r="A88" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C88" s="1">
         <v>2043.14</v>
       </c>
       <c r="D88" s="1">
-        <v>2750.729999999999</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4">
+        <v>2750.73</v>
+      </c>
+      <c r="E88" s="1">
+        <v>2221.36</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
       <c r="A89" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C89" s="1">
         <v>7144.959999999999</v>
       </c>
       <c r="D89" s="1">
-        <v>5865.03</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4">
+        <v>5865.029999999999</v>
+      </c>
+      <c r="E89" s="1">
+        <v>8175.429999999998</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
       <c r="A90" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C90" s="1">
-        <v>3425.09</v>
+        <v>3425.089999999999</v>
       </c>
       <c r="D90" s="1">
-        <v>3419.239999999999</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4">
+        <v>3419.24</v>
+      </c>
+      <c r="E90" s="1">
+        <v>3520.949999999999</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
       <c r="A91" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C91" s="1">
-        <v>4159.059999999999</v>
+        <v>4159.059999999998</v>
       </c>
       <c r="D91" s="1">
-        <v>4600.06</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4">
+        <v>4600.059999999999</v>
+      </c>
+      <c r="E91" s="1">
+        <v>4977.339999999998</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
       <c r="A92" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C92" s="1">
         <v>1419.14</v>
@@ -2217,65 +2493,83 @@
       <c r="D92" s="1">
         <v>1359.84</v>
       </c>
-    </row>
-    <row r="93" spans="1:4">
+      <c r="E92" s="1">
+        <v>1221.87</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
       <c r="A93" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C93" s="1">
-        <v>6690.219999999998</v>
+        <v>6690.220000000001</v>
       </c>
       <c r="D93" s="1">
-        <v>4262.5</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4">
+        <v>4262.499999999999</v>
+      </c>
+      <c r="E93" s="1">
+        <v>4885.009999999998</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
       <c r="A94" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C94" s="1">
         <v>5898.499999999999</v>
       </c>
       <c r="D94" s="1">
-        <v>8525.119999999997</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4">
+        <v>8525.119999999999</v>
+      </c>
+      <c r="E94" s="1">
+        <v>6033.009999999998</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
       <c r="A95" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C95" s="1">
         <v>4024.239999999999</v>
       </c>
       <c r="D95" s="1">
-        <v>5659.279999999999</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4">
+        <v>5659.279999999998</v>
+      </c>
+      <c r="E95" s="1">
+        <v>4563.279999999999</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
       <c r="A96" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C96" s="1">
-        <v>5956.62</v>
+        <v>5956.619999999997</v>
       </c>
       <c r="D96" s="1">
-        <v>6697.92</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4">
+        <v>6697.919999999997</v>
+      </c>
+      <c r="E96" s="1">
+        <v>9399.529999999997</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
       <c r="A97" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C97" s="1">
-        <v>4705.809999999998</v>
+        <v>4705.809999999999</v>
       </c>
       <c r="D97" s="1">
         <v>4194.48</v>
       </c>
-    </row>
-    <row r="98" spans="1:4">
+      <c r="E97" s="1">
+        <v>5642.909999999999</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
       <c r="A98" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C98" s="1">
         <v>2528.93</v>
@@ -2283,10 +2577,13 @@
       <c r="D98" s="1">
         <v>2142.34</v>
       </c>
-    </row>
-    <row r="99" spans="1:4">
+      <c r="E98" s="1">
+        <v>1322.09</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
       <c r="A99" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C99" s="1">
         <v>1629.63</v>
@@ -2294,87 +2591,111 @@
       <c r="D99" s="1">
         <v>1654.78</v>
       </c>
-    </row>
-    <row r="100" spans="1:4">
+      <c r="E99" s="1">
+        <v>1070.87</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
       <c r="A100" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C100" s="1">
-        <v>3986.559999999999</v>
+        <v>3986.56</v>
       </c>
       <c r="D100" s="1">
-        <v>3449.319999999999</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4">
+        <v>3449.32</v>
+      </c>
+      <c r="E100" s="1">
+        <v>1700.71</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
       <c r="A101" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C101" s="1">
         <v>3869.84</v>
       </c>
       <c r="D101" s="1">
-        <v>6719.559999999999</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4">
+        <v>6719.559999999998</v>
+      </c>
+      <c r="E101" s="1">
+        <v>5557.349999999998</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5">
       <c r="A102" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C102" s="1">
-        <v>3383.49</v>
+        <v>3383.489999999999</v>
       </c>
       <c r="D102" s="1">
-        <v>4209.269999999999</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4">
+        <v>4209.27</v>
+      </c>
+      <c r="E102" s="1">
+        <v>3044.939999999999</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5">
       <c r="A103" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C103" s="1">
         <v>2240.88</v>
       </c>
       <c r="D103" s="1">
-        <v>3074.84</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4">
+        <v>3074.840000000001</v>
+      </c>
+      <c r="E103" s="1">
+        <v>1711.07</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5">
       <c r="A104" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C104" s="1">
-        <v>3977.579999999999</v>
+        <v>3977.579999999998</v>
       </c>
       <c r="D104" s="1">
         <v>3341.63</v>
       </c>
-    </row>
-    <row r="105" spans="1:4">
+      <c r="E104" s="1">
+        <v>1741.57</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5">
       <c r="A105" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C105" s="1">
         <v>3610.409999999999</v>
       </c>
       <c r="D105" s="1">
-        <v>5104.049999999999</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4">
+        <v>5104.049999999998</v>
+      </c>
+      <c r="E105" s="1">
+        <v>2985.669999999999</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5">
       <c r="A106" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C106" s="1">
-        <v>2172.98</v>
+        <v>2172.979999999999</v>
       </c>
       <c r="D106" s="1">
-        <v>3653.299999999999</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4">
+        <v>3653.3</v>
+      </c>
+      <c r="E106" s="1">
+        <v>2405.829999999999</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5">
       <c r="A107" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C107" s="1">
         <v>3074</v>
@@ -2382,32 +2703,41 @@
       <c r="D107" s="1">
         <v>2594.75</v>
       </c>
-    </row>
-    <row r="108" spans="1:4">
+      <c r="E107" s="1">
+        <v>2955.799999999999</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5">
       <c r="A108" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C108" s="1">
-        <v>3212.449999999999</v>
+        <v>3212.45</v>
       </c>
       <c r="D108" s="1">
         <v>1897.88</v>
       </c>
-    </row>
-    <row r="109" spans="1:4">
+      <c r="E108" s="1">
+        <v>3167.810000000001</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5">
       <c r="A109" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C109" s="1">
-        <v>2623.949999999999</v>
+        <v>2623.95</v>
       </c>
       <c r="D109" s="1">
         <v>684.96</v>
       </c>
-    </row>
-    <row r="110" spans="1:4">
+      <c r="E109" s="1">
+        <v>2150.38</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5">
       <c r="A110" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C110" s="1">
         <v>1840.38</v>
@@ -2415,10 +2745,13 @@
       <c r="D110" s="1">
         <v>1826.09</v>
       </c>
-    </row>
-    <row r="111" spans="1:4">
+      <c r="E110" s="1">
+        <v>2029.38</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5">
       <c r="A111" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C111" s="1">
         <v>1153.03</v>
@@ -2426,10 +2759,13 @@
       <c r="D111" s="1">
         <v>1052.97</v>
       </c>
-    </row>
-    <row r="112" spans="1:4">
+      <c r="E111" s="1">
+        <v>1148.87</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5">
       <c r="A112" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C112" s="1">
         <v>2730.76</v>
@@ -2437,10 +2773,13 @@
       <c r="D112" s="1">
         <v>3764.669999999999</v>
       </c>
-    </row>
-    <row r="113" spans="1:4">
+      <c r="E112" s="1">
+        <v>3926.05</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5">
       <c r="A113" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C113" s="1">
         <v>753.55</v>
@@ -2448,10 +2787,13 @@
       <c r="D113" s="1">
         <v>1127.67</v>
       </c>
-    </row>
-    <row r="114" spans="1:4">
+      <c r="E113" s="1">
+        <v>853.3900000000001</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5">
       <c r="A114" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C114" s="1">
         <v>1985.69</v>
@@ -2459,10 +2801,13 @@
       <c r="D114" s="1">
         <v>1091.39</v>
       </c>
-    </row>
-    <row r="115" spans="1:4">
+      <c r="E114" s="1">
+        <v>2218.75</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5">
       <c r="A115" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C115" s="1">
         <v>1962.42</v>
@@ -2470,10 +2815,13 @@
       <c r="D115" s="1">
         <v>1350.44</v>
       </c>
-    </row>
-    <row r="116" spans="1:4">
+      <c r="E115" s="1">
+        <v>1818.14</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5">
       <c r="A116" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C116" s="1">
         <v>4071.73</v>
@@ -2481,10 +2829,13 @@
       <c r="D116" s="1">
         <v>2351.59</v>
       </c>
-    </row>
-    <row r="117" spans="1:4">
+      <c r="E116" s="1">
+        <v>4349.47</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5">
       <c r="A117" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C117" s="1">
         <v>3250.52</v>
@@ -2492,21 +2843,27 @@
       <c r="D117" s="1">
         <v>1185.48</v>
       </c>
-    </row>
-    <row r="118" spans="1:4">
+      <c r="E117" s="1">
+        <v>1968.53</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5">
       <c r="A118" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C118" s="1">
-        <v>6771.53</v>
+        <v>6771.529999999999</v>
       </c>
       <c r="D118" s="1">
-        <v>4554.49</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4">
+        <v>4554.489999999999</v>
+      </c>
+      <c r="E118" s="1">
+        <v>4393.67</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5">
       <c r="A119" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C119" s="1">
         <v>3170.929999999999</v>
@@ -2514,21 +2871,27 @@
       <c r="D119" s="1">
         <v>2057.51</v>
       </c>
-    </row>
-    <row r="120" spans="1:4">
+      <c r="E119" s="1">
+        <v>3161.78</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5">
       <c r="A120" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C120" s="1">
-        <v>4395.329999999999</v>
+        <v>4395.33</v>
       </c>
       <c r="D120" s="1">
         <v>4956.559999999999</v>
       </c>
-    </row>
-    <row r="121" spans="1:4">
+      <c r="E120" s="1">
+        <v>3166.34</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5">
       <c r="A121" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C121" s="1">
         <v>3018.189999999999</v>
@@ -2536,21 +2899,27 @@
       <c r="D121" s="1">
         <v>3813.48</v>
       </c>
-    </row>
-    <row r="122" spans="1:4">
+      <c r="E121" s="1">
+        <v>4437.459999999998</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5">
       <c r="A122" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C122" s="1">
         <v>2914.57</v>
       </c>
       <c r="D122" s="1">
-        <v>2510.819999999999</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4">
+        <v>2510.82</v>
+      </c>
+      <c r="E122" s="1">
+        <v>3067.23</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5">
       <c r="A123" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C123" s="1">
         <v>2419.93</v>
@@ -2558,10 +2927,13 @@
       <c r="D123" s="1">
         <v>2272.23</v>
       </c>
-    </row>
-    <row r="124" spans="1:4">
+      <c r="E123" s="1">
+        <v>2004.74</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5">
       <c r="A124" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C124" s="1">
         <v>4381.049999999999</v>
@@ -2569,32 +2941,41 @@
       <c r="D124" s="1">
         <v>3206.419999999999</v>
       </c>
-    </row>
-    <row r="125" spans="1:4">
+      <c r="E124" s="1">
+        <v>3161.839999999998</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5">
       <c r="A125" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C125" s="1">
         <v>2755.999999999999</v>
       </c>
       <c r="D125" s="1">
-        <v>2903.619999999999</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4">
+        <v>2903.62</v>
+      </c>
+      <c r="E125" s="1">
+        <v>2924.17</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5">
       <c r="A126" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C126" s="1">
-        <v>3260.299999999999</v>
+        <v>3260.3</v>
       </c>
       <c r="D126" s="1">
         <v>3466.41</v>
       </c>
-    </row>
-    <row r="127" spans="1:4">
+      <c r="E126" s="1">
+        <v>2249.04</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5">
       <c r="A127" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C127" s="1">
         <v>4049.359999999999</v>
@@ -2602,32 +2983,41 @@
       <c r="D127" s="1">
         <v>3507.37</v>
       </c>
-    </row>
-    <row r="128" spans="1:4">
+      <c r="E127" s="1">
+        <v>1041.6</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5">
       <c r="A128" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C128" s="1">
-        <v>2897.3</v>
+        <v>2897.299999999999</v>
       </c>
       <c r="D128" s="1">
-        <v>4238.39</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4">
+        <v>4238.389999999999</v>
+      </c>
+      <c r="E128" s="1">
+        <v>2512.33</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5">
       <c r="A129" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C129" s="1">
         <v>8782.450000000001</v>
       </c>
       <c r="D129" s="1">
-        <v>9309.009999999997</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4">
+        <v>9409</v>
+      </c>
+      <c r="E129" s="1">
+        <v>6285.14</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5">
       <c r="A130" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C130" s="1">
         <v>467.9400000000001</v>
@@ -2635,10 +3025,13 @@
       <c r="D130" s="1">
         <v>992.75</v>
       </c>
-    </row>
-    <row r="131" spans="1:4">
+      <c r="E130" s="1">
+        <v>1409.87</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5">
       <c r="A131" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C131" s="1">
         <v>3594.84</v>
@@ -2646,21 +3039,27 @@
       <c r="D131" s="1">
         <v>2862.22</v>
       </c>
-    </row>
-    <row r="132" spans="1:4">
+      <c r="E131" s="1">
+        <v>2551.23</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5">
       <c r="A132" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C132" s="1">
-        <v>6140.69</v>
+        <v>6140.689999999999</v>
       </c>
       <c r="D132" s="1">
         <v>6191.469999999998</v>
       </c>
-    </row>
-    <row r="133" spans="1:4">
+      <c r="E132" s="1">
+        <v>6162.439999999999</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5">
       <c r="A133" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C133" s="1">
         <v>3869.439999999999</v>
@@ -2668,21 +3067,27 @@
       <c r="D133" s="1">
         <v>4460.309999999999</v>
       </c>
-    </row>
-    <row r="134" spans="1:4">
+      <c r="E133" s="1">
+        <v>5055.619999999999</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5">
       <c r="A134" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C134" s="1">
-        <v>5167.87</v>
+        <v>5167.869999999999</v>
       </c>
       <c r="D134" s="1">
         <v>4090.909999999999</v>
       </c>
-    </row>
-    <row r="135" spans="1:4">
+      <c r="E134" s="1">
+        <v>4849.179999999999</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5">
       <c r="A135" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C135" s="1">
         <v>2067.91</v>
@@ -2690,65 +3095,83 @@
       <c r="D135" s="1">
         <v>1450.25</v>
       </c>
-    </row>
-    <row r="136" spans="1:4">
+      <c r="E135" s="1">
+        <v>2501.38</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5">
       <c r="A136" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C136" s="1">
-        <v>5151.88</v>
+        <v>5151.879999999999</v>
       </c>
       <c r="D136" s="1">
         <v>6352.949999999999</v>
       </c>
-    </row>
-    <row r="137" spans="1:4">
+      <c r="E136" s="1">
+        <v>5489.319999999999</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5">
       <c r="A137" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C137" s="1">
         <v>3687.21</v>
       </c>
       <c r="D137" s="1">
-        <v>3191.53</v>
-      </c>
-    </row>
-    <row r="138" spans="1:4">
+        <v>3191.530000000001</v>
+      </c>
+      <c r="E137" s="1">
+        <v>4032.099999999999</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5">
       <c r="A138" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C138" s="1">
-        <v>5207.739999999999</v>
+        <v>5207.74</v>
       </c>
       <c r="D138" s="1">
-        <v>3956.07</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4">
+        <v>3956.069999999999</v>
+      </c>
+      <c r="E138" s="1">
+        <v>4011.219999999999</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5">
       <c r="A139" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C139" s="1">
         <v>9087.759999999998</v>
       </c>
       <c r="D139" s="1">
-        <v>7234.02</v>
-      </c>
-    </row>
-    <row r="140" spans="1:4">
+        <v>7234.019999999999</v>
+      </c>
+      <c r="E139" s="1">
+        <v>7292.58</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5">
       <c r="A140" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C140" s="1">
-        <v>4924.459999999999</v>
+        <v>4924.459999999998</v>
       </c>
       <c r="D140" s="1">
         <v>6991.709999999999</v>
       </c>
-    </row>
-    <row r="141" spans="1:4">
+      <c r="E140" s="1">
+        <v>4369.739999999999</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5">
       <c r="A141" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C141" s="1">
         <v>2057.44</v>
@@ -2756,10 +3179,13 @@
       <c r="D141" s="1">
         <v>2228.4</v>
       </c>
-    </row>
-    <row r="142" spans="1:4">
+      <c r="E141" s="1">
+        <v>2436.26</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5">
       <c r="A142" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C142" s="1">
         <v>1729.72</v>
@@ -2767,21 +3193,27 @@
       <c r="D142" s="1">
         <v>834.12</v>
       </c>
-    </row>
-    <row r="143" spans="1:4">
+      <c r="E142" s="1">
+        <v>2733.18</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5">
       <c r="A143" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C143" s="1">
-        <v>4052.900000000001</v>
+        <v>4052.899999999999</v>
       </c>
       <c r="D143" s="1">
         <v>3174.909999999999</v>
       </c>
-    </row>
-    <row r="144" spans="1:4">
+      <c r="E143" s="1">
+        <v>4170.049999999998</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5">
       <c r="A144" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C144" s="1">
         <v>1444.51</v>
@@ -2789,10 +3221,13 @@
       <c r="D144" s="1">
         <v>2346.72</v>
       </c>
-    </row>
-    <row r="145" spans="1:4">
+      <c r="E144" s="1">
+        <v>893.8099999999999</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5">
       <c r="A145" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C145" s="1">
         <v>1319.12</v>
@@ -2800,10 +3235,13 @@
       <c r="D145" s="1">
         <v>1383.47</v>
       </c>
-    </row>
-    <row r="146" spans="1:4">
+      <c r="E145" s="1">
+        <v>1673.7</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5">
       <c r="A146" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C146" s="1">
         <v>3014.489999999999</v>
@@ -2811,10 +3249,13 @@
       <c r="D146" s="1">
         <v>2656.15</v>
       </c>
-    </row>
-    <row r="147" spans="1:4">
+      <c r="E146" s="1">
+        <v>2645.899999999999</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5">
       <c r="A147" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C147" s="1">
         <v>1909.14</v>
@@ -2822,54 +3263,69 @@
       <c r="D147" s="1">
         <v>2821.809999999999</v>
       </c>
-    </row>
-    <row r="148" spans="1:4">
+      <c r="E147" s="1">
+        <v>2691.659999999999</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5">
       <c r="A148" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C148" s="1">
-        <v>6420.53</v>
+        <v>6420.529999999999</v>
       </c>
       <c r="D148" s="1">
-        <v>5555.649999999999</v>
-      </c>
-    </row>
-    <row r="149" spans="1:4">
+        <v>5555.65</v>
+      </c>
+      <c r="E148" s="1">
+        <v>5694.520000000001</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5">
       <c r="A149" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C149" s="1">
         <v>1629.52</v>
       </c>
       <c r="D149" s="1">
-        <v>949.9000000000001</v>
-      </c>
-    </row>
-    <row r="150" spans="1:4">
+        <v>949.8999999999999</v>
+      </c>
+      <c r="E149" s="1">
+        <v>498.76</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5">
       <c r="A150" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C150" s="1">
-        <v>4523.839999999998</v>
+        <v>4604.829999999999</v>
       </c>
       <c r="D150" s="1">
         <v>4561.219999999999</v>
       </c>
-    </row>
-    <row r="151" spans="1:4">
+      <c r="E150" s="1">
+        <v>6881.469999999998</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5">
       <c r="A151" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C151" s="1">
         <v>4199.98</v>
       </c>
       <c r="D151" s="1">
-        <v>4454.91</v>
-      </c>
-    </row>
-    <row r="152" spans="1:4">
+        <v>4454.909999999999</v>
+      </c>
+      <c r="E151" s="1">
+        <v>4469.719999999999</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5">
       <c r="A152" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C152" s="1">
         <v>4719.9</v>
@@ -2877,21 +3333,27 @@
       <c r="D152" s="1">
         <v>3408.26</v>
       </c>
-    </row>
-    <row r="153" spans="1:4">
+      <c r="E152" s="1">
+        <v>4028.46</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5">
       <c r="A153" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C153" s="1">
-        <v>5029.429999999999</v>
+        <v>5029.429999999998</v>
       </c>
       <c r="D153" s="1">
         <v>5167.889999999999</v>
       </c>
-    </row>
-    <row r="154" spans="1:4">
+      <c r="E153" s="1">
+        <v>4689.879999999998</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5">
       <c r="A154" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C154" s="1">
         <v>3525.52</v>
@@ -2899,32 +3361,41 @@
       <c r="D154" s="1">
         <v>7125.009999999998</v>
       </c>
-    </row>
-    <row r="155" spans="1:4">
+      <c r="E154" s="1">
+        <v>7132.71</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5">
       <c r="A155" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C155" s="1">
-        <v>4059.679999999999</v>
+        <v>4059.68</v>
       </c>
       <c r="D155" s="1">
         <v>3503.24</v>
       </c>
-    </row>
-    <row r="156" spans="1:4">
+      <c r="E155" s="1">
+        <v>3902.109999999999</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5">
       <c r="A156" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C156" s="1">
-        <v>6928.979999999998</v>
+        <v>6928.979999999999</v>
       </c>
       <c r="D156" s="1">
         <v>4116.249999999999</v>
       </c>
-    </row>
-    <row r="157" spans="1:4">
+      <c r="E156" s="1">
+        <v>5112.54</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5">
       <c r="A157" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C157" s="1">
         <v>3606.32</v>
@@ -2932,43 +3403,55 @@
       <c r="D157" s="1">
         <v>3794.659999999999</v>
       </c>
-    </row>
-    <row r="158" spans="1:4">
+      <c r="E157" s="1">
+        <v>4819.32</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5">
       <c r="A158" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C158" s="1">
-        <v>6345.329999999999</v>
+        <v>6345.33</v>
       </c>
       <c r="D158" s="1">
-        <v>4842.509999999999</v>
-      </c>
-    </row>
-    <row r="159" spans="1:4">
+        <v>4842.509999999998</v>
+      </c>
+      <c r="E158" s="1">
+        <v>6207.819999999998</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5">
       <c r="A159" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C159" s="1">
-        <v>7418.239999999999</v>
+        <v>7418.24</v>
       </c>
       <c r="D159" s="1">
         <v>4001.46</v>
       </c>
-    </row>
-    <row r="160" spans="1:4">
+      <c r="E159" s="1">
+        <v>7350.330000000001</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5">
       <c r="A160" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C160" s="1">
         <v>7671.06</v>
       </c>
       <c r="D160" s="1">
-        <v>4597.46</v>
-      </c>
-    </row>
-    <row r="161" spans="1:4">
+        <v>4597.459999999999</v>
+      </c>
+      <c r="E160" s="1">
+        <v>6447.39</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5">
       <c r="A161" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C161" s="1">
         <v>1420.27</v>
@@ -2976,21 +3459,27 @@
       <c r="D161" s="1">
         <v>1986.84</v>
       </c>
-    </row>
-    <row r="162" spans="1:4">
+      <c r="E161" s="1">
+        <v>1002.75</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5">
       <c r="A162" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C162" s="1">
-        <v>3101.549999999999</v>
+        <v>3101.55</v>
       </c>
       <c r="D162" s="1">
         <v>3045.239999999999</v>
       </c>
-    </row>
-    <row r="163" spans="1:4">
+      <c r="E162" s="1">
+        <v>1733.87</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5">
       <c r="A163" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C163" s="1">
         <v>2793</v>
@@ -2998,32 +3487,41 @@
       <c r="D163" s="1">
         <v>1452.26</v>
       </c>
-    </row>
-    <row r="164" spans="1:4">
+      <c r="E163" s="1">
+        <v>3630.01</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5">
       <c r="A164" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C164" s="1">
-        <v>3666.1</v>
+        <v>3666.099999999999</v>
       </c>
       <c r="D164" s="1">
-        <v>5508.989999999999</v>
-      </c>
-    </row>
-    <row r="165" spans="1:4">
+        <v>5508.990000000001</v>
+      </c>
+      <c r="E164" s="1">
+        <v>6156.299999999998</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5">
       <c r="A165" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C165" s="1">
-        <v>2780.42</v>
+        <v>2780.419999999999</v>
       </c>
       <c r="D165" s="1">
-        <v>3319.119999999998</v>
-      </c>
-    </row>
-    <row r="166" spans="1:4">
+        <v>3319.12</v>
+      </c>
+      <c r="E165" s="1">
+        <v>2358.93</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5">
       <c r="A166" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C166" s="1">
         <v>12699.61</v>
@@ -3031,98 +3529,125 @@
       <c r="D166" s="1">
         <v>13801.95</v>
       </c>
-    </row>
-    <row r="167" spans="1:4">
+      <c r="E166" s="1">
+        <v>13439.74</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5">
       <c r="A167" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C167" s="1">
-        <v>2942.399999999999</v>
+        <v>2942.4</v>
       </c>
       <c r="D167" s="1">
         <v>2718.809999999999</v>
       </c>
-    </row>
-    <row r="168" spans="1:4">
+      <c r="E167" s="1">
+        <v>773.6999999999998</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5">
       <c r="A168" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C168" s="1">
-        <v>8936.269999999999</v>
+        <v>8936.270000000002</v>
       </c>
       <c r="D168" s="1">
-        <v>6341.019999999996</v>
-      </c>
-    </row>
-    <row r="169" spans="1:4">
+        <v>6341.02</v>
+      </c>
+      <c r="E168" s="1">
+        <v>8562.5</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5">
       <c r="A169" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C169" s="1">
         <v>2312.47</v>
       </c>
       <c r="D169" s="1">
-        <v>2768.4</v>
-      </c>
-    </row>
-    <row r="170" spans="1:4">
+        <v>2768.400000000001</v>
+      </c>
+      <c r="E169" s="1">
+        <v>1437.52</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5">
       <c r="A170" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C170" s="1">
         <v>3127.939999999999</v>
       </c>
       <c r="D170" s="1">
-        <v>2894.879999999999</v>
-      </c>
-    </row>
-    <row r="171" spans="1:4">
+        <v>2894.88</v>
+      </c>
+      <c r="E170" s="1">
+        <v>4686.599999999999</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5">
       <c r="A171" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C171" s="1">
         <v>5234.86</v>
       </c>
       <c r="D171" s="1">
-        <v>5613.129999999999</v>
-      </c>
-    </row>
-    <row r="172" spans="1:4">
+        <v>5613.129999999998</v>
+      </c>
+      <c r="E171" s="1">
+        <v>4286.13</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5">
       <c r="A172" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C172" s="1">
         <v>7472.959999999999</v>
       </c>
       <c r="D172" s="1">
-        <v>8474.93</v>
-      </c>
-    </row>
-    <row r="173" spans="1:4">
+        <v>8474.929999999998</v>
+      </c>
+      <c r="E172" s="1">
+        <v>5804.529999999999</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5">
       <c r="A173" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C173" s="1">
-        <v>4585.139999999999</v>
+        <v>4585.139999999998</v>
       </c>
       <c r="D173" s="1">
         <v>3528.579999999999</v>
       </c>
-    </row>
-    <row r="174" spans="1:4">
+      <c r="E173" s="1">
+        <v>3838.949999999999</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5">
       <c r="A174" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C174" s="1">
-        <v>3328.859999999999</v>
+        <v>3328.86</v>
       </c>
       <c r="D174" s="1">
         <v>2990.609999999999</v>
       </c>
-    </row>
-    <row r="175" spans="1:4">
+      <c r="E174" s="1">
+        <v>3844.12</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5">
       <c r="A175" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C175" s="1">
         <v>3267.27</v>
@@ -3130,21 +3655,27 @@
       <c r="D175" s="1">
         <v>1491.67</v>
       </c>
-    </row>
-    <row r="176" spans="1:4">
+      <c r="E175" s="1">
+        <v>3034.379999999999</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5">
       <c r="A176" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C176" s="1">
-        <v>2753.62</v>
+        <v>2753.619999999999</v>
       </c>
       <c r="D176" s="1">
         <v>2511.84</v>
       </c>
-    </row>
-    <row r="177" spans="1:4">
+      <c r="E176" s="1">
+        <v>2413.4</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5">
       <c r="A177" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C177" s="1">
         <v>3715.3</v>
@@ -3152,10 +3683,13 @@
       <c r="D177" s="1">
         <v>3752.179999999999</v>
       </c>
-    </row>
-    <row r="178" spans="1:4">
+      <c r="E177" s="1">
+        <v>2451.749999999999</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5">
       <c r="A178" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C178" s="1">
         <v>1563.81</v>
@@ -3163,21 +3697,27 @@
       <c r="D178" s="1">
         <v>1483.77</v>
       </c>
-    </row>
-    <row r="179" spans="1:4">
+      <c r="E178" s="1">
+        <v>897.77</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5">
       <c r="A179" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C179" s="1">
-        <v>2753.459999999999</v>
+        <v>2753.460000000001</v>
       </c>
       <c r="D179" s="1">
         <v>2985.139999999999</v>
       </c>
-    </row>
-    <row r="180" spans="1:4">
+      <c r="E179" s="1">
+        <v>1651.33</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5">
       <c r="A180" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C180" s="1">
         <v>1093.87</v>
@@ -3185,10 +3725,13 @@
       <c r="D180" s="1">
         <v>2766.72</v>
       </c>
-    </row>
-    <row r="181" spans="1:4">
+      <c r="E180" s="1">
+        <v>2279.74</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5">
       <c r="A181" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C181" s="1">
         <v>1962.53</v>
@@ -3196,43 +3739,55 @@
       <c r="D181" s="1">
         <v>2443.18</v>
       </c>
-    </row>
-    <row r="182" spans="1:4">
+      <c r="E181" s="1">
+        <v>1202.77</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5">
       <c r="A182" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C182" s="1">
         <v>3963.5</v>
       </c>
       <c r="D182" s="1">
-        <v>5577.720000000001</v>
-      </c>
-    </row>
-    <row r="183" spans="1:4">
+        <v>5577.719999999999</v>
+      </c>
+      <c r="E182" s="1">
+        <v>4628.859999999999</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5">
       <c r="A183" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C183" s="1">
-        <v>4886.889999999998</v>
+        <v>4886.889999999999</v>
       </c>
       <c r="D183" s="1">
-        <v>5822.309999999999</v>
-      </c>
-    </row>
-    <row r="184" spans="1:4">
+        <v>5822.31</v>
+      </c>
+      <c r="E183" s="1">
+        <v>5399.279999999998</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5">
       <c r="A184" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C184" s="1">
         <v>6729.119999999999</v>
       </c>
       <c r="D184" s="1">
-        <v>9562.139999999998</v>
-      </c>
-    </row>
-    <row r="185" spans="1:4">
+        <v>9562.139999999999</v>
+      </c>
+      <c r="E184" s="1">
+        <v>6666.939999999999</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5">
       <c r="A185" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C185" s="1">
         <v>3096.75</v>
@@ -3240,43 +3795,55 @@
       <c r="D185" s="1">
         <v>2879.68</v>
       </c>
-    </row>
-    <row r="186" spans="1:4">
+      <c r="E185" s="1">
+        <v>1515.78</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5">
       <c r="A186" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C186" s="1">
         <v>3772.669999999999</v>
       </c>
       <c r="D186" s="1">
-        <v>3613.879999999999</v>
-      </c>
-    </row>
-    <row r="187" spans="1:4">
+        <v>3613.879999999998</v>
+      </c>
+      <c r="E186" s="1">
+        <v>3475.579999999999</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5">
       <c r="A187" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C187" s="1">
         <v>10902.5</v>
       </c>
       <c r="D187" s="1">
-        <v>11239.73</v>
-      </c>
-    </row>
-    <row r="188" spans="1:4">
+        <v>11239.73000000001</v>
+      </c>
+      <c r="E187" s="1">
+        <v>11888.49</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5">
       <c r="A188" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C188" s="1">
-        <v>5446.049999999999</v>
+        <v>5446.05</v>
       </c>
       <c r="D188" s="1">
         <v>4955.54</v>
       </c>
-    </row>
-    <row r="189" spans="1:4">
+      <c r="E188" s="1">
+        <v>6492.839999999998</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5">
       <c r="A189" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C189" s="1">
         <v>2757.74</v>
@@ -3284,10 +3851,13 @@
       <c r="D189" s="1">
         <v>2274.65</v>
       </c>
-    </row>
-    <row r="190" spans="1:4">
+      <c r="E189" s="1">
+        <v>4160.34</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5">
       <c r="A190" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C190" s="1">
         <v>1194.78</v>
@@ -3295,10 +3865,13 @@
       <c r="D190" s="1">
         <v>1775.63</v>
       </c>
-    </row>
-    <row r="191" spans="1:4">
+      <c r="E190" s="1">
+        <v>1381.69</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5">
       <c r="A191" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C191" s="1">
         <v>1844.56</v>
@@ -3306,43 +3879,55 @@
       <c r="D191" s="1">
         <v>1390.87</v>
       </c>
-    </row>
-    <row r="192" spans="1:4">
+      <c r="E191" s="1">
+        <v>2503.44</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5">
       <c r="A192" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C192" s="1">
-        <v>5137.889999999999</v>
+        <v>5137.89</v>
       </c>
       <c r="D192" s="1">
         <v>5349.849999999999</v>
       </c>
-    </row>
-    <row r="193" spans="1:4">
+      <c r="E192" s="1">
+        <v>4216.389999999999</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5">
       <c r="A193" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C193" s="1">
-        <v>5213.78</v>
+        <v>5213.779999999998</v>
       </c>
       <c r="D193" s="1">
-        <v>9210.4</v>
-      </c>
-    </row>
-    <row r="194" spans="1:4">
+        <v>9210.399999999998</v>
+      </c>
+      <c r="E193" s="1">
+        <v>6294.489999999999</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5">
       <c r="A194" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C194" s="1">
-        <v>4397.61</v>
+        <v>4397.609999999999</v>
       </c>
       <c r="D194" s="1">
         <v>6347.41</v>
       </c>
-    </row>
-    <row r="195" spans="1:4">
+      <c r="E194" s="1">
+        <v>7570.020000000001</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5">
       <c r="A195" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C195" s="1">
         <v>2168.48</v>
@@ -3350,32 +3935,41 @@
       <c r="D195" s="1">
         <v>4061.48</v>
       </c>
-    </row>
-    <row r="196" spans="1:4">
+      <c r="E195" s="1">
+        <v>2983.05</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5">
       <c r="A196" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C196" s="1">
         <v>9386.089999999998</v>
       </c>
       <c r="D196" s="1">
-        <v>7981.969999999998</v>
-      </c>
-    </row>
-    <row r="197" spans="1:4">
+        <v>7981.97</v>
+      </c>
+      <c r="E196" s="1">
+        <v>9296.209999999999</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5">
       <c r="A197" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C197" s="1">
         <v>5896.049999999998</v>
       </c>
       <c r="D197" s="1">
-        <v>5611.469999999999</v>
-      </c>
-    </row>
-    <row r="198" spans="1:4">
+        <v>5611.469999999998</v>
+      </c>
+      <c r="E197" s="1">
+        <v>6104.079999999999</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5">
       <c r="A198" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C198" s="1">
         <v>1107.72</v>
@@ -3383,10 +3977,13 @@
       <c r="D198" s="1">
         <v>2147.43</v>
       </c>
-    </row>
-    <row r="199" spans="1:4">
+      <c r="E198" s="1">
+        <v>1024.44</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5">
       <c r="A199" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C199" s="1">
         <v>2399.79</v>
@@ -3394,21 +3991,27 @@
       <c r="D199" s="1">
         <v>1863.24</v>
       </c>
-    </row>
-    <row r="200" spans="1:4">
+      <c r="E199" s="1">
+        <v>2059.89</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5">
       <c r="A200" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C200" s="1">
-        <v>6225.41</v>
+        <v>6225.409999999997</v>
       </c>
       <c r="D200" s="1">
-        <v>7749.430000000001</v>
-      </c>
-    </row>
-    <row r="201" spans="1:4">
+        <v>7758.419999999999</v>
+      </c>
+      <c r="E200" s="1">
+        <v>7738.15</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5">
       <c r="A201" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C201" s="1">
         <v>2888.04</v>
@@ -3416,10 +4019,13 @@
       <c r="D201" s="1">
         <v>3018.119999999999</v>
       </c>
-    </row>
-    <row r="202" spans="1:4">
+      <c r="E201" s="1">
+        <v>2735.129999999999</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5">
       <c r="A202" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C202" s="1">
         <v>2186.65</v>
@@ -3427,10 +4033,13 @@
       <c r="D202" s="1">
         <v>1400.23</v>
       </c>
-    </row>
-    <row r="203" spans="1:4">
+      <c r="E202" s="1">
+        <v>1315.16</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5">
       <c r="A203" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C203" s="1">
         <v>665.23</v>
@@ -3438,21 +4047,27 @@
       <c r="D203" s="1">
         <v>764.9400000000001</v>
       </c>
-    </row>
-    <row r="204" spans="1:4">
+      <c r="E203" s="1">
+        <v>102.64</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5">
       <c r="A204" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C204" s="1">
         <v>1503.76</v>
       </c>
       <c r="D204" s="1">
-        <v>1295.51</v>
-      </c>
-    </row>
-    <row r="205" spans="1:4">
+        <v>1528.5</v>
+      </c>
+      <c r="E204" s="1">
+        <v>1610.67</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5">
       <c r="A205" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C205" s="1">
         <v>1873.98</v>
@@ -3460,10 +4075,13 @@
       <c r="D205" s="1">
         <v>1956.18</v>
       </c>
-    </row>
-    <row r="206" spans="1:4">
+      <c r="E205" s="1">
+        <v>1535.87</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5">
       <c r="A206" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C206" s="1">
         <v>1051.48</v>
@@ -3471,21 +4089,27 @@
       <c r="D206" s="1">
         <v>1844.28</v>
       </c>
-    </row>
-    <row r="207" spans="1:4">
+      <c r="E206" s="1">
+        <v>1209.74</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5">
       <c r="A207" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C207" s="1">
-        <v>2871.97</v>
+        <v>2871.969999999999</v>
       </c>
       <c r="D207" s="1">
         <v>2313.150000000001</v>
       </c>
-    </row>
-    <row r="208" spans="1:4">
+      <c r="E207" s="1">
+        <v>1635.89</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5">
       <c r="A208" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C208" s="1">
         <v>1929.64</v>
@@ -3493,43 +4117,55 @@
       <c r="D208" s="1">
         <v>1179.72</v>
       </c>
-    </row>
-    <row r="209" spans="1:4">
+      <c r="E208" s="1">
+        <v>700.02</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5">
       <c r="A209" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C209" s="1">
         <v>3807.93</v>
       </c>
       <c r="D209" s="1">
-        <v>4191.339999999998</v>
-      </c>
-    </row>
-    <row r="210" spans="1:4">
+        <v>4191.339999999999</v>
+      </c>
+      <c r="E209" s="1">
+        <v>3075.74</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5">
       <c r="A210" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C210" s="1">
-        <v>2466.079999999999</v>
+        <v>2466.08</v>
       </c>
       <c r="D210" s="1">
         <v>3171.21</v>
       </c>
-    </row>
-    <row r="211" spans="1:4">
+      <c r="E210" s="1">
+        <v>3405.419999999999</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5">
       <c r="A211" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C211" s="1">
-        <v>5620.46</v>
+        <v>5620.459999999999</v>
       </c>
       <c r="D211" s="1">
-        <v>3655.319999999999</v>
-      </c>
-    </row>
-    <row r="212" spans="1:4">
+        <v>3655.32</v>
+      </c>
+      <c r="E211" s="1">
+        <v>3600.49</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5">
       <c r="A212" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C212" s="1">
         <v>3801.99</v>
@@ -3537,10 +4173,13 @@
       <c r="D212" s="1">
         <v>2592.31</v>
       </c>
-    </row>
-    <row r="213" spans="1:4">
+      <c r="E212" s="1">
+        <v>1574.33</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5">
       <c r="A213" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C213" s="1">
         <v>787.21</v>
@@ -3548,43 +4187,55 @@
       <c r="D213" s="1">
         <v>1471.64</v>
       </c>
-    </row>
-    <row r="214" spans="1:4">
+      <c r="E213" s="1">
+        <v>1098.77</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5">
       <c r="A214" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C214" s="1">
         <v>3913.579999999999</v>
       </c>
       <c r="D214" s="1">
-        <v>4222.26</v>
-      </c>
-    </row>
-    <row r="215" spans="1:4">
+        <v>4222.259999999999</v>
+      </c>
+      <c r="E214" s="1">
+        <v>4700.55</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5">
       <c r="A215" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C215" s="1">
-        <v>2738.469999999998</v>
+        <v>2738.469999999999</v>
       </c>
       <c r="D215" s="1">
         <v>1353.38</v>
       </c>
-    </row>
-    <row r="216" spans="1:4">
+      <c r="E215" s="1">
+        <v>2205.77</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5">
       <c r="A216" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C216" s="1">
         <v>1452.4</v>
       </c>
       <c r="D216" s="1">
-        <v>514.7</v>
-      </c>
-    </row>
-    <row r="217" spans="1:4">
+        <v>514.6999999999999</v>
+      </c>
+      <c r="E216" s="1">
+        <v>1012.96</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5">
       <c r="A217" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C217" s="1">
         <v>1797.68</v>
@@ -3592,10 +4243,13 @@
       <c r="D217" s="1">
         <v>2012.03</v>
       </c>
-    </row>
-    <row r="218" spans="1:4">
+      <c r="E217" s="1">
+        <v>1504.89</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5">
       <c r="A218" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C218" s="1">
         <v>2601.44</v>
@@ -3603,10 +4257,13 @@
       <c r="D218" s="1">
         <v>1602.68</v>
       </c>
-    </row>
-    <row r="219" spans="1:4">
+      <c r="E218" s="1">
+        <v>1883.69</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5">
       <c r="A219" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C219" s="1">
         <v>995.77</v>
@@ -3614,87 +4271,111 @@
       <c r="D219" s="1">
         <v>1027.31</v>
       </c>
-    </row>
-    <row r="220" spans="1:4">
+      <c r="E219" s="1">
+        <v>1553.81</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5">
       <c r="A220" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C220" s="1">
-        <v>2747.06</v>
+        <v>2747.059999999999</v>
       </c>
       <c r="D220" s="1">
         <v>2927.26</v>
       </c>
-    </row>
-    <row r="221" spans="1:4">
+      <c r="E220" s="1">
+        <v>3010.419999999999</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5">
       <c r="A221" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C221" s="1">
-        <v>6881.5</v>
+        <v>6881.499999999999</v>
       </c>
       <c r="D221" s="1">
         <v>5413.389999999999</v>
       </c>
-    </row>
-    <row r="222" spans="1:4">
+      <c r="E221" s="1">
+        <v>6178.189999999999</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5">
       <c r="A222" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C222" s="1">
-        <v>3662.279999999999</v>
+        <v>3662.28</v>
       </c>
       <c r="D222" s="1">
-        <v>4521.849999999999</v>
-      </c>
-    </row>
-    <row r="223" spans="1:4">
+        <v>4521.85</v>
+      </c>
+      <c r="E222" s="1">
+        <v>3518.82</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5">
       <c r="A223" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C223" s="1">
-        <v>3532.81</v>
+        <v>3532.810000000001</v>
       </c>
       <c r="D223" s="1">
-        <v>4711.570000000001</v>
-      </c>
-    </row>
-    <row r="224" spans="1:4">
+        <v>4711.569999999999</v>
+      </c>
+      <c r="E223" s="1">
+        <v>6409.13</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5">
       <c r="A224" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C224" s="1">
         <v>1565.21</v>
       </c>
       <c r="D224" s="1">
-        <v>2797.969999999999</v>
-      </c>
-    </row>
-    <row r="225" spans="1:4">
+        <v>2797.97</v>
+      </c>
+      <c r="E224" s="1">
+        <v>1503.79</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5">
       <c r="A225" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C225" s="1">
-        <v>4006.29</v>
+        <v>4006.289999999999</v>
       </c>
       <c r="D225" s="1">
         <v>3379.53</v>
       </c>
-    </row>
-    <row r="226" spans="1:4">
+      <c r="E225" s="1">
+        <v>2266.3</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5">
       <c r="A226" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C226" s="1">
-        <v>4844.289999999999</v>
+        <v>4844.289999999998</v>
       </c>
       <c r="D226" s="1">
-        <v>4802.349999999999</v>
-      </c>
-    </row>
-    <row r="227" spans="1:4">
+        <v>4802.35</v>
+      </c>
+      <c r="E226" s="1">
+        <v>2749.06</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5">
       <c r="A227" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C227" s="1">
         <v>2534.96</v>
@@ -3702,65 +4383,83 @@
       <c r="D227" s="1">
         <v>3326.48</v>
       </c>
-    </row>
-    <row r="228" spans="1:4">
+      <c r="E227" s="1">
+        <v>2583.509999999998</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5">
       <c r="A228" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C228" s="1">
-        <v>2639.119999999999</v>
+        <v>2639.12</v>
       </c>
       <c r="D228" s="1">
         <v>2509.32</v>
       </c>
-    </row>
-    <row r="229" spans="1:4">
+      <c r="E228" s="1">
+        <v>1765.97</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5">
       <c r="A229" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C229" s="1">
         <v>1816.960000000001</v>
       </c>
       <c r="D229" s="1">
-        <v>3279.889999999999</v>
-      </c>
-    </row>
-    <row r="230" spans="1:4">
+        <v>3279.89</v>
+      </c>
+      <c r="E229" s="1">
+        <v>2858.04</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5">
       <c r="A230" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C230" s="1">
         <v>2240.06</v>
       </c>
       <c r="D230" s="1">
-        <v>3348.78</v>
-      </c>
-    </row>
-    <row r="231" spans="1:4">
+        <v>3348.779999999999</v>
+      </c>
+      <c r="E230" s="1">
+        <v>1677.19</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5">
       <c r="A231" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C231" s="1">
-        <v>4579.72</v>
+        <v>4579.719999999998</v>
       </c>
       <c r="D231" s="1">
-        <v>3825.549999999998</v>
-      </c>
-    </row>
-    <row r="232" spans="1:4">
+        <v>3825.549999999999</v>
+      </c>
+      <c r="E231" s="1">
+        <v>3672.75</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5">
       <c r="A232" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C232" s="1">
         <v>3810.389999999999</v>
       </c>
       <c r="D232" s="1">
-        <v>6474.16</v>
-      </c>
-    </row>
-    <row r="233" spans="1:4">
+        <v>6474.159999999997</v>
+      </c>
+      <c r="E232" s="1">
+        <v>2143.98</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5">
       <c r="A233" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C233" s="1">
         <v>3889.849999999999</v>
@@ -3768,10 +4467,13 @@
       <c r="D233" s="1">
         <v>3758.329999999999</v>
       </c>
-    </row>
-    <row r="234" spans="1:4">
+      <c r="E233" s="1">
+        <v>4819.849999999999</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5">
       <c r="A234" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C234" s="1">
         <v>2410.34</v>
@@ -3779,54 +4481,69 @@
       <c r="D234" s="1">
         <v>3411.32</v>
       </c>
-    </row>
-    <row r="235" spans="1:4">
+      <c r="E234" s="1">
+        <v>2657.019999999999</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5">
       <c r="A235" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C235" s="1">
-        <v>2652.879999999999</v>
+        <v>2652.88</v>
       </c>
       <c r="D235" s="1">
         <v>2544.41</v>
       </c>
-    </row>
-    <row r="236" spans="1:4">
+      <c r="E235" s="1">
+        <v>3059.77</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5">
       <c r="A236" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C236" s="1">
-        <v>4375.249999999999</v>
+        <v>4375.249999999998</v>
       </c>
       <c r="D236" s="1">
-        <v>2525.66</v>
-      </c>
-    </row>
-    <row r="237" spans="1:4">
+        <v>2525.659999999999</v>
+      </c>
+      <c r="E236" s="1">
+        <v>4483.059999999999</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5">
       <c r="A237" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C237" s="1">
         <v>1872.3</v>
       </c>
       <c r="D237" s="1">
-        <v>3275.6</v>
-      </c>
-    </row>
-    <row r="238" spans="1:4">
+        <v>3275.599999999999</v>
+      </c>
+      <c r="E237" s="1">
+        <v>3164.529999999999</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5">
       <c r="A238" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C238" s="1">
-        <v>2454.88</v>
+        <v>2454.880000000001</v>
       </c>
       <c r="D238" s="1">
         <v>3054.55</v>
       </c>
-    </row>
-    <row r="239" spans="1:4">
+      <c r="E238" s="1">
+        <v>3080.52</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5">
       <c r="A239" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C239" s="1">
         <v>2753.279999999999</v>
@@ -3834,10 +4551,13 @@
       <c r="D239" s="1">
         <v>2583.98</v>
       </c>
-    </row>
-    <row r="240" spans="1:4">
+      <c r="E239" s="1">
+        <v>2366.22</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5">
       <c r="A240" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C240" s="1">
         <v>1583.29</v>
@@ -3845,32 +4565,41 @@
       <c r="D240" s="1">
         <v>2581.04</v>
       </c>
-    </row>
-    <row r="241" spans="1:4">
+      <c r="E240" s="1">
+        <v>1973.62</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5">
       <c r="A241" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C241" s="1">
-        <v>6251.02</v>
+        <v>6251.019999999998</v>
       </c>
       <c r="D241" s="1">
-        <v>5878.609999999998</v>
-      </c>
-    </row>
-    <row r="242" spans="1:4">
+        <v>5878.61</v>
+      </c>
+      <c r="E241" s="1">
+        <v>5328.629999999998</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5">
       <c r="A242" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C242" s="1">
-        <v>2472.599999999999</v>
+        <v>2472.6</v>
       </c>
       <c r="D242" s="1">
         <v>2228.72</v>
       </c>
-    </row>
-    <row r="243" spans="1:4">
+      <c r="E242" s="1">
+        <v>5354.379999999998</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5">
       <c r="A243" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C243" s="1">
         <v>2894.96</v>
@@ -3878,21 +4607,27 @@
       <c r="D243" s="1">
         <v>3649.929999999999</v>
       </c>
-    </row>
-    <row r="244" spans="1:4">
+      <c r="E243" s="1">
+        <v>3365.899999999999</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5">
       <c r="A244" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C244" s="1">
         <v>5758.889999999998</v>
       </c>
       <c r="D244" s="1">
-        <v>4799.589999999999</v>
-      </c>
-    </row>
-    <row r="245" spans="1:4">
+        <v>4888.579999999998</v>
+      </c>
+      <c r="E244" s="1">
+        <v>6086.509999999998</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5">
       <c r="A245" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C245" s="1">
         <v>6043.14</v>
@@ -3900,43 +4635,55 @@
       <c r="D245" s="1">
         <v>4923.429999999999</v>
       </c>
-    </row>
-    <row r="246" spans="1:4">
+      <c r="E245" s="1">
+        <v>4516.969999999999</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5">
       <c r="A246" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C246" s="1">
-        <v>3040.229999999999</v>
+        <v>3040.23</v>
       </c>
       <c r="D246" s="1">
-        <v>3793.759999999999</v>
-      </c>
-    </row>
-    <row r="247" spans="1:4">
+        <v>3793.76</v>
+      </c>
+      <c r="E246" s="1">
+        <v>2084.45</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5">
       <c r="A247" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C247" s="1">
-        <v>8001.68</v>
+        <v>8001.679999999998</v>
       </c>
       <c r="D247" s="1">
-        <v>9167.819999999998</v>
-      </c>
-    </row>
-    <row r="248" spans="1:4">
+        <v>9167.820000000002</v>
+      </c>
+      <c r="E247" s="1">
+        <v>5383.129999999998</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5">
       <c r="A248" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C248" s="1">
         <v>4437.239999999999</v>
       </c>
       <c r="D248" s="1">
-        <v>4629.09</v>
-      </c>
-    </row>
-    <row r="249" spans="1:4">
+        <v>4629.089999999999</v>
+      </c>
+      <c r="E248" s="1">
+        <v>2318.509999999999</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5">
       <c r="A249" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C249" s="1">
         <v>13494.29</v>
@@ -3944,10 +4691,13 @@
       <c r="D249" s="1">
         <v>12032.23</v>
       </c>
-    </row>
-    <row r="250" spans="1:4">
+      <c r="E249" s="1">
+        <v>15660.62</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5">
       <c r="A250" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C250" s="1">
         <v>2017.83</v>
@@ -3955,10 +4705,13 @@
       <c r="D250" s="1">
         <v>1392.49</v>
       </c>
-    </row>
-    <row r="251" spans="1:4">
+      <c r="E250" s="1">
+        <v>1228.62</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5">
       <c r="A251" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C251" s="1">
         <v>1344.87</v>
@@ -3966,43 +4719,55 @@
       <c r="D251" s="1">
         <v>912.22</v>
       </c>
-    </row>
-    <row r="252" spans="1:4">
+      <c r="E251" s="1">
+        <v>1235.2</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5">
       <c r="A252" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C252" s="1">
         <v>3071.79</v>
       </c>
       <c r="D252" s="1">
-        <v>3475.06</v>
-      </c>
-    </row>
-    <row r="253" spans="1:4">
+        <v>3475.059999999999</v>
+      </c>
+      <c r="E252" s="1">
+        <v>4932.650000000001</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5">
       <c r="A253" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C253" s="1">
-        <v>2342.32</v>
+        <v>2342.319999999999</v>
       </c>
       <c r="D253" s="1">
         <v>1218.68</v>
       </c>
-    </row>
-    <row r="254" spans="1:4">
+      <c r="E253" s="1">
+        <v>1687.69</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5">
       <c r="A254" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C254" s="1">
-        <v>9315.109999999999</v>
+        <v>9315.109999999997</v>
       </c>
       <c r="D254" s="1">
         <v>6063.68</v>
       </c>
-    </row>
-    <row r="255" spans="1:4">
+      <c r="E254" s="1">
+        <v>8401.189999999999</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5">
       <c r="A255" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C255" s="1">
         <v>1633.9</v>
@@ -4010,10 +4775,13 @@
       <c r="D255" s="1">
         <v>1921.88</v>
       </c>
-    </row>
-    <row r="256" spans="1:4">
+      <c r="E255" s="1">
+        <v>1685.17</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5">
       <c r="A256" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C256" s="1">
         <v>3603.309999999999</v>
@@ -4021,43 +4789,55 @@
       <c r="D256" s="1">
         <v>3526.52</v>
       </c>
-    </row>
-    <row r="257" spans="1:4">
+      <c r="E256" s="1">
+        <v>3578.310000000001</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5">
       <c r="A257" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C257" s="1">
         <v>2316.88</v>
       </c>
       <c r="D257" s="1">
-        <v>892.7399999999999</v>
-      </c>
-    </row>
-    <row r="258" spans="1:4">
+        <v>892.74</v>
+      </c>
+      <c r="E257" s="1">
+        <v>2789.82</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5">
       <c r="A258" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C258" s="1">
-        <v>4147.279999999999</v>
+        <v>4147.28</v>
       </c>
       <c r="D258" s="1">
         <v>3475.189999999999</v>
       </c>
-    </row>
-    <row r="259" spans="1:4">
+      <c r="E258" s="1">
+        <v>3076.18</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5">
       <c r="A259" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C259" s="1">
-        <v>4881.710000000001</v>
+        <v>4881.71</v>
       </c>
       <c r="D259" s="1">
         <v>6327.37</v>
       </c>
-    </row>
-    <row r="260" spans="1:4">
+      <c r="E259" s="1">
+        <v>6746.039999999999</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5">
       <c r="A260" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C260" s="1">
         <v>2063.96</v>
@@ -4065,10 +4845,13 @@
       <c r="D260" s="1">
         <v>2522.32</v>
       </c>
-    </row>
-    <row r="261" spans="1:4">
+      <c r="E260" s="1">
+        <v>2008.37</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5">
       <c r="A261" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C261" s="1">
         <v>10140.64</v>
@@ -4076,54 +4859,69 @@
       <c r="D261" s="1">
         <v>10191.47</v>
       </c>
-    </row>
-    <row r="262" spans="1:4">
+      <c r="E261" s="1">
+        <v>8889.599999999997</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5">
       <c r="A262" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C262" s="1">
         <v>6590.969999999998</v>
       </c>
       <c r="D262" s="1">
-        <v>6377.889999999998</v>
-      </c>
-    </row>
-    <row r="263" spans="1:4">
+        <v>6377.889999999999</v>
+      </c>
+      <c r="E262" s="1">
+        <v>3236.469999999999</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5">
       <c r="A263" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C263" s="1">
-        <v>3060.099999999999</v>
+        <v>3060.100000000001</v>
       </c>
       <c r="D263" s="1">
         <v>3799.149999999999</v>
       </c>
-    </row>
-    <row r="264" spans="1:4">
+      <c r="E263" s="1">
+        <v>2534.98</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5">
       <c r="A264" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C264" s="1">
         <v>11492.78</v>
       </c>
       <c r="D264" s="1">
-        <v>9176.83</v>
-      </c>
-    </row>
-    <row r="265" spans="1:4">
+        <v>9176.829999999996</v>
+      </c>
+      <c r="E264" s="1">
+        <v>11039.58</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5">
       <c r="A265" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C265" s="1">
-        <v>9339.840000000002</v>
+        <v>9339.839999999998</v>
       </c>
       <c r="D265" s="1">
-        <v>8478.709999999999</v>
-      </c>
-    </row>
-    <row r="266" spans="1:4">
+        <v>8478.710000000001</v>
+      </c>
+      <c r="E265" s="1">
+        <v>8800.649999999998</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5">
       <c r="A266" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C266" s="1">
         <v>2908.369999999999</v>
@@ -4131,21 +4929,27 @@
       <c r="D266" s="1">
         <v>1748.42</v>
       </c>
-    </row>
-    <row r="267" spans="1:4">
+      <c r="E266" s="1">
+        <v>5317.089999999998</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5">
       <c r="A267" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C267" s="1">
-        <v>2829.689999999999</v>
+        <v>2829.69</v>
       </c>
       <c r="D267" s="1">
         <v>2970.43</v>
       </c>
-    </row>
-    <row r="268" spans="1:4">
+      <c r="E267" s="1">
+        <v>1976.09</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5">
       <c r="A268" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C268" s="1">
         <v>1493.04</v>
@@ -4153,16 +4957,22 @@
       <c r="D268" s="1">
         <v>1168.55</v>
       </c>
-    </row>
-    <row r="269" spans="1:4">
+      <c r="E268" s="1">
+        <v>910.39</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5">
       <c r="A269" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C269" s="1">
         <v>434.11</v>
       </c>
       <c r="D269" s="1">
         <v>606.3900000000001</v>
+      </c>
+      <c r="E269" s="1">
+        <v>512.05</v>
       </c>
     </row>
   </sheetData>
